--- a/results/data/semih_async_balanced_dqn_experiment_results.xlsx
+++ b/results/data/semih_async_balanced_dqn_experiment_results.xlsx
@@ -750,190 +750,190 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>103.5</v>
+        <v>81.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.201562118716424</v>
+        <v>41.63231917633222</v>
       </c>
       <c r="D2" t="n">
-        <v>106.6</v>
+        <v>99</v>
       </c>
       <c r="E2" t="n">
-        <v>5.370288632839022</v>
+        <v>25.57342370508884</v>
       </c>
       <c r="F2" t="n">
-        <v>103.5</v>
+        <v>107.7</v>
       </c>
       <c r="G2" t="n">
-        <v>7.566372975210778</v>
+        <v>2.193171219946131</v>
       </c>
       <c r="H2" t="n">
-        <v>104.5</v>
+        <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>6.88839603971781</v>
+        <v>1.61245154965971</v>
       </c>
       <c r="J2" t="n">
-        <v>114</v>
+        <v>108.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2.144761058952722</v>
+        <v>1.57797338380595</v>
       </c>
       <c r="L2" t="n">
-        <v>113.7</v>
+        <v>110.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.531797780234432</v>
+        <v>1.962141687034858</v>
       </c>
       <c r="N2" t="n">
-        <v>113.8</v>
+        <v>109</v>
       </c>
       <c r="O2" t="n">
-        <v>2.959729717389748</v>
+        <v>1.341640786499874</v>
       </c>
       <c r="P2" t="n">
-        <v>113.6</v>
+        <v>109.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.168595903550972</v>
+        <v>2.051828452868319</v>
       </c>
       <c r="R2" t="n">
-        <v>113.6</v>
+        <v>109.9</v>
       </c>
       <c r="S2" t="n">
-        <v>4.431703961232068</v>
+        <v>1.86815416922694</v>
       </c>
       <c r="T2" t="n">
-        <v>112.8</v>
+        <v>109.7</v>
       </c>
       <c r="U2" t="n">
-        <v>6.925315877272314</v>
+        <v>2.147091055358389</v>
       </c>
       <c r="V2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W2" t="n">
-        <v>5.118593556827891</v>
+        <v>1.183215956619923</v>
       </c>
       <c r="X2" t="n">
-        <v>109.2</v>
+        <v>110.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.166589146867567</v>
+        <v>1.813835714721705</v>
       </c>
       <c r="Z2" t="n">
-        <v>108.6</v>
+        <v>110.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.825599018605541</v>
+        <v>1.268857754044952</v>
       </c>
       <c r="AB2" t="n">
-        <v>104.1</v>
+        <v>110.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.449161026585477</v>
+        <v>1.939071942966532</v>
       </c>
       <c r="AD2" t="n">
-        <v>106.6</v>
+        <v>110.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>8.333066662399863</v>
+        <v>2.521904042583698</v>
       </c>
       <c r="AF2" t="n">
-        <v>108.6</v>
+        <v>111.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.3072789813801</v>
+        <v>2.244994432064364</v>
       </c>
       <c r="AH2" t="n">
-        <v>101.1</v>
+        <v>112.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.803675477269621</v>
+        <v>1.688194301613413</v>
       </c>
       <c r="AJ2" t="n">
-        <v>102.9</v>
+        <v>112.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.670082458260917</v>
+        <v>1.57797338380595</v>
       </c>
       <c r="AL2" t="n">
-        <v>103.7</v>
+        <v>113.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.798295289429651</v>
+        <v>3.269556544854363</v>
       </c>
       <c r="AN2" t="n">
-        <v>105.2</v>
+        <v>114.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.44796630928718</v>
+        <v>1.857417562100671</v>
       </c>
       <c r="AP2" t="n">
-        <v>99.3</v>
+        <v>116.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.335529974037323</v>
+        <v>2.467792535850613</v>
       </c>
       <c r="AR2" t="n">
-        <v>98.40000000000001</v>
+        <v>117.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.425863986500215</v>
+        <v>2.521904042583698</v>
       </c>
       <c r="AT2" t="n">
-        <v>100.2</v>
+        <v>117.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.354308211415448</v>
+        <v>2.521904042583698</v>
       </c>
       <c r="AV2" t="n">
-        <v>98.8</v>
+        <v>120.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.919183588453085</v>
+        <v>5.080354318352216</v>
       </c>
       <c r="AX2" t="n">
-        <v>98</v>
+        <v>123.8</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.049691346263317</v>
+        <v>6.749814812274482</v>
       </c>
       <c r="AZ2" t="n">
-        <v>99.2</v>
+        <v>126.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.764613810115105</v>
+        <v>6.63023378170031</v>
       </c>
       <c r="BB2" t="n">
-        <v>108.1</v>
+        <v>124.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.272551134230683</v>
+        <v>2.147091055358389</v>
       </c>
       <c r="BD2" t="n">
-        <v>99.7</v>
+        <v>127.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.473253849269008</v>
+        <v>6.356886030125127</v>
       </c>
       <c r="BF2" t="n">
-        <v>99.5</v>
+        <v>136.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.15223536610881</v>
+        <v>9.055937278934744</v>
       </c>
       <c r="BH2" t="n">
-        <v>106</v>
+        <v>138.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>7.523297149521611</v>
+        <v>9.594269122762817</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3165.799999999999</v>
+        <v>3420.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>105.5266666666666</v>
+        <v>114.0166666666667</v>
       </c>
     </row>
     <row r="3">
@@ -941,190 +941,190 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>104</v>
+        <v>98.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3.741657386773941</v>
+        <v>24.92087478400387</v>
       </c>
       <c r="D3" t="n">
-        <v>108.5</v>
+        <v>99.3</v>
       </c>
       <c r="E3" t="n">
-        <v>3.827531841800928</v>
+        <v>26.85535328384268</v>
       </c>
       <c r="F3" t="n">
-        <v>109.4</v>
+        <v>108.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6946778377222</v>
+        <v>2.374868417407583</v>
       </c>
       <c r="H3" t="n">
-        <v>105.8</v>
+        <v>108.3</v>
       </c>
       <c r="I3" t="n">
-        <v>7.934733769950949</v>
+        <v>1.345362404707371</v>
       </c>
       <c r="J3" t="n">
-        <v>111.6</v>
+        <v>100.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.693237062523878</v>
+        <v>25.64293274959009</v>
       </c>
       <c r="L3" t="n">
-        <v>113.3</v>
+        <v>108.9</v>
       </c>
       <c r="M3" t="n">
-        <v>6.419501538281613</v>
+        <v>2.022374841615668</v>
       </c>
       <c r="N3" t="n">
-        <v>106.2</v>
+        <v>110.2</v>
       </c>
       <c r="O3" t="n">
-        <v>11.22319027727856</v>
+        <v>1.4</v>
       </c>
       <c r="P3" t="n">
-        <v>116.8</v>
+        <v>110.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.886796226411321</v>
+        <v>1.813835714721705</v>
       </c>
       <c r="R3" t="n">
-        <v>114.9</v>
+        <v>108.7</v>
       </c>
       <c r="S3" t="n">
-        <v>3.858756276314947</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>113.8</v>
+        <v>109.6</v>
       </c>
       <c r="U3" t="n">
-        <v>6.852736679604726</v>
+        <v>1.907878402833891</v>
       </c>
       <c r="V3" t="n">
-        <v>114.3</v>
+        <v>110.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.637708029332781</v>
+        <v>1.8</v>
       </c>
       <c r="X3" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.097617696340303</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.98997487421324</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>112</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.408318915758459</v>
+      </c>
+      <c r="AD3" t="n">
         <v>112.3</v>
       </c>
-      <c r="Y3" t="n">
-        <v>7.510659092250159</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>110.7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6.309516621738942</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.487638069569178</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>103</v>
-      </c>
       <c r="AE3" t="n">
-        <v>9.736529155710468</v>
+        <v>1.615549442140351</v>
       </c>
       <c r="AF3" t="n">
-        <v>108.3</v>
+        <v>111.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>9.980480950335009</v>
+        <v>1.833030277982336</v>
       </c>
       <c r="AH3" t="n">
-        <v>104.9</v>
+        <v>112.3</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.529276193632426</v>
+        <v>1.791647286716892</v>
       </c>
       <c r="AJ3" t="n">
-        <v>104.3</v>
+        <v>114</v>
       </c>
       <c r="AK3" t="n">
-        <v>7.82368199762746</v>
+        <v>1.843908891458578</v>
       </c>
       <c r="AL3" t="n">
-        <v>103.7</v>
+        <v>114.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>8.414867794564572</v>
+        <v>2.376972864800943</v>
       </c>
       <c r="AN3" t="n">
-        <v>97.59999999999999</v>
+        <v>117.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.6946778377222</v>
+        <v>6.00416522091123</v>
       </c>
       <c r="AP3" t="n">
-        <v>100.1</v>
+        <v>115.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.503635162326805</v>
+        <v>1.907878402833891</v>
       </c>
       <c r="AR3" t="n">
-        <v>101.3</v>
+        <v>118.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.820997676000147</v>
+        <v>2.537715508089904</v>
       </c>
       <c r="AT3" t="n">
-        <v>101</v>
+        <v>119.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.366563145999495</v>
+        <v>2.135415650406262</v>
       </c>
       <c r="AV3" t="n">
-        <v>102.3</v>
+        <v>120.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.74299345444258</v>
+        <v>1.22065556157337</v>
       </c>
       <c r="AX3" t="n">
-        <v>101.8</v>
+        <v>122.6</v>
       </c>
       <c r="AY3" t="n">
+        <v>1.854723699099141</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.562049935181331</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.858571279792899</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.384355879804947</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.838388161361178</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>7.85175139698144</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>8.558621384311845</v>
-      </c>
       <c r="BF3" t="n">
-        <v>105.5</v>
+        <v>133.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.00416522091123</v>
+        <v>11.00181803158005</v>
       </c>
       <c r="BH3" t="n">
-        <v>103.1</v>
+        <v>141.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>7.930321557162737</v>
+        <v>10.59433811051922</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3191.4</v>
+        <v>3437.3</v>
       </c>
       <c r="BK3" t="n">
-        <v>106.38</v>
+        <v>114.5766666666667</v>
       </c>
     </row>
     <row r="4">
@@ -1132,190 +1132,190 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>105.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>3.762977544445356</v>
+        <v>35.62920150662936</v>
       </c>
       <c r="D4" t="n">
-        <v>108.6</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>4.673328578219168</v>
+        <v>35.06693599389602</v>
       </c>
       <c r="F4" t="n">
-        <v>108</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4.427188724235731</v>
+        <v>41.98916526915009</v>
       </c>
       <c r="H4" t="n">
-        <v>107.5</v>
+        <v>108.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7.459892760623306</v>
+        <v>2.973213749463701</v>
       </c>
       <c r="J4" t="n">
-        <v>107.4</v>
+        <v>99.3</v>
       </c>
       <c r="K4" t="n">
-        <v>8.834025130143111</v>
+        <v>25.48744789106983</v>
       </c>
       <c r="L4" t="n">
-        <v>111.2</v>
+        <v>108.8</v>
       </c>
       <c r="M4" t="n">
-        <v>7.56042326857432</v>
+        <v>2.227105745132008</v>
       </c>
       <c r="N4" t="n">
-        <v>115</v>
+        <v>110.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.483239697419133</v>
+        <v>2.202271554554524</v>
       </c>
       <c r="P4" t="n">
-        <v>112.4</v>
+        <v>110.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.755738301621816</v>
+        <v>2.521904042583698</v>
       </c>
       <c r="R4" t="n">
-        <v>112.8</v>
+        <v>111</v>
       </c>
       <c r="S4" t="n">
-        <v>6.144916598294887</v>
+        <v>2.190890230020664</v>
       </c>
       <c r="T4" t="n">
-        <v>111.1</v>
+        <v>110</v>
       </c>
       <c r="U4" t="n">
-        <v>9.23525852372309</v>
+        <v>1.897366596101028</v>
       </c>
       <c r="V4" t="n">
-        <v>111.4</v>
+        <v>110.8</v>
       </c>
       <c r="W4" t="n">
-        <v>6.053098380168622</v>
+        <v>2.271563338320109</v>
       </c>
       <c r="X4" t="n">
-        <v>107.7</v>
+        <v>110</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.450581369148055</v>
+        <v>2.366431913239846</v>
       </c>
       <c r="Z4" t="n">
-        <v>109</v>
+        <v>111.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.48074069840786</v>
+        <v>2.765863337187866</v>
       </c>
       <c r="AB4" t="n">
-        <v>112.8</v>
+        <v>110</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.337191807101944</v>
+        <v>2.449489742783178</v>
       </c>
       <c r="AD4" t="n">
-        <v>103.1</v>
+        <v>110.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>6.905794668247818</v>
+        <v>1.813835714721705</v>
       </c>
       <c r="AF4" t="n">
-        <v>105.7</v>
+        <v>112.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.29611577246488</v>
+        <v>1.615549442140351</v>
       </c>
       <c r="AH4" t="n">
-        <v>104.8</v>
+        <v>112.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.516301802696256</v>
+        <v>2.271563338320109</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99.8</v>
+        <v>114.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>6.939740629158989</v>
+        <v>2.376972864800943</v>
       </c>
       <c r="AL4" t="n">
-        <v>107.2</v>
+        <v>114.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>10.89770618066022</v>
+        <v>2.467792535850613</v>
       </c>
       <c r="AN4" t="n">
-        <v>97.7</v>
+        <v>116.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.282542442102665</v>
+        <v>6.305553108173778</v>
       </c>
       <c r="AP4" t="n">
-        <v>100</v>
+        <v>116.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.60357029044876</v>
+        <v>2.655183609470351</v>
       </c>
       <c r="AR4" t="n">
-        <v>101.9</v>
+        <v>118.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.008991914547277</v>
+        <v>2.247220505424423</v>
       </c>
       <c r="AT4" t="n">
-        <v>100.7</v>
+        <v>120.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.388270501473776</v>
+        <v>6.200806399170999</v>
       </c>
       <c r="AV4" t="n">
-        <v>100.1</v>
+        <v>123.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.948737212663449</v>
+        <v>8.653900854527974</v>
       </c>
       <c r="AX4" t="n">
-        <v>102.6</v>
+        <v>126.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.003332407921454</v>
+        <v>8.309031231136396</v>
       </c>
       <c r="AZ4" t="n">
-        <v>103</v>
+        <v>126.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.714835124201342</v>
+        <v>6.523802572120036</v>
       </c>
       <c r="BB4" t="n">
-        <v>102.3</v>
+        <v>126</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.622277118748239</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>103</v>
+        <v>128.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.692099788303083</v>
+        <v>6.496922348312315</v>
       </c>
       <c r="BF4" t="n">
-        <v>101.9</v>
+        <v>133.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.664803615307419</v>
+        <v>7.419568720619818</v>
       </c>
       <c r="BH4" t="n">
-        <v>106.3</v>
+        <v>140.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>7.40337760755184</v>
+        <v>10.72567014223354</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3180.2</v>
+        <v>3395.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>106.0066666666667</v>
+        <v>113.1833333333333</v>
       </c>
     </row>
     <row r="5">
@@ -1323,190 +1323,190 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>104.2</v>
+        <v>81.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.026549190084311</v>
+        <v>38.87685686883651</v>
       </c>
       <c r="D5" t="n">
-        <v>104.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>4.369210454990695</v>
+        <v>26.01710975492858</v>
       </c>
       <c r="F5" t="n">
-        <v>108.2</v>
+        <v>101.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.236021006050217</v>
+        <v>26.09003641239314</v>
       </c>
       <c r="H5" t="n">
-        <v>110.9</v>
+        <v>109.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.913760456866693</v>
+        <v>1.959591794226542</v>
       </c>
       <c r="J5" t="n">
-        <v>111</v>
+        <v>109.1</v>
       </c>
       <c r="K5" t="n">
-        <v>7.810249675906654</v>
+        <v>1.972308292331602</v>
       </c>
       <c r="L5" t="n">
-        <v>112.6</v>
+        <v>108.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.907878402833891</v>
+        <v>1.920937271229854</v>
       </c>
       <c r="N5" t="n">
-        <v>114.7</v>
+        <v>110.3</v>
       </c>
       <c r="O5" t="n">
-        <v>7.000714249274855</v>
+        <v>1.9</v>
       </c>
       <c r="P5" t="n">
-        <v>112.7</v>
+        <v>109.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.723838189605696</v>
+        <v>2.385372088375313</v>
       </c>
       <c r="R5" t="n">
-        <v>117.2</v>
+        <v>110</v>
       </c>
       <c r="S5" t="n">
-        <v>2.891366458960193</v>
+        <v>2.32379000772445</v>
       </c>
       <c r="T5" t="n">
-        <v>110.3</v>
+        <v>111.2</v>
       </c>
       <c r="U5" t="n">
-        <v>7.836453279386026</v>
+        <v>1.32664991614216</v>
       </c>
       <c r="V5" t="n">
-        <v>111.7</v>
+        <v>109.8</v>
       </c>
       <c r="W5" t="n">
-        <v>8.888756943465156</v>
+        <v>1.98997487421324</v>
       </c>
       <c r="X5" t="n">
-        <v>109.1</v>
+        <v>109.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.275868534480233</v>
+        <v>2.451530134426252</v>
       </c>
       <c r="Z5" t="n">
-        <v>104.5</v>
+        <v>111.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.902897942168926</v>
+        <v>1.98997487421324</v>
       </c>
       <c r="AB5" t="n">
-        <v>106.5</v>
+        <v>111.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.87386354243376</v>
+        <v>2.0591260281974</v>
       </c>
       <c r="AD5" t="n">
-        <v>102.1</v>
+        <v>112.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>7.034912934784622</v>
+        <v>2.418677324489565</v>
       </c>
       <c r="AF5" t="n">
-        <v>100.4</v>
+        <v>110.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.135144660071187</v>
+        <v>2.181742422927143</v>
       </c>
       <c r="AH5" t="n">
-        <v>104.4</v>
+        <v>112.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.916646586316233</v>
+        <v>1.16619037896906</v>
       </c>
       <c r="AJ5" t="n">
-        <v>103.2</v>
+        <v>114.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>9.836666101886349</v>
+        <v>2.325940669922601</v>
       </c>
       <c r="AL5" t="n">
-        <v>103.7</v>
+        <v>114.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.295179322956194</v>
+        <v>2.794637722496424</v>
       </c>
       <c r="AN5" t="n">
-        <v>98.8</v>
+        <v>114</v>
       </c>
       <c r="AO5" t="n">
-        <v>7.717512552629895</v>
+        <v>2.097617696340303</v>
       </c>
       <c r="AP5" t="n">
-        <v>102.9</v>
+        <v>118</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.03131905077539</v>
+        <v>6.767569726275452</v>
       </c>
       <c r="AR5" t="n">
-        <v>104.2</v>
+        <v>116.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.249827584156743</v>
+        <v>1.676305461424021</v>
       </c>
       <c r="AT5" t="n">
-        <v>101.1</v>
+        <v>120.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.489325737341114</v>
+        <v>2.947880594596735</v>
       </c>
       <c r="AV5" t="n">
-        <v>101</v>
+        <v>124.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.774934554525329</v>
+        <v>8.742997197757758</v>
       </c>
       <c r="AX5" t="n">
-        <v>105.6</v>
+        <v>126</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.134549797335389</v>
+        <v>5.118593556827891</v>
       </c>
       <c r="AZ5" t="n">
-        <v>102.6</v>
+        <v>128.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.270831300812524</v>
+        <v>8.355237878121724</v>
       </c>
       <c r="BB5" t="n">
-        <v>101.8</v>
+        <v>129.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.912698199637793</v>
+        <v>7.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>106.6</v>
+        <v>127.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.295280917949491</v>
+        <v>5.723635208501674</v>
       </c>
       <c r="BF5" t="n">
-        <v>101.3</v>
+        <v>142.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.550496672405067</v>
+        <v>11.08557621416226</v>
       </c>
       <c r="BH5" t="n">
-        <v>106.2</v>
+        <v>137.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>7.846018098373213</v>
+        <v>10.37496987947435</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3183.6</v>
+        <v>3440.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>106.12</v>
+        <v>114.6933333333333</v>
       </c>
     </row>
     <row r="6">
@@ -1514,190 +1514,190 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>103.3</v>
+        <v>89.8</v>
       </c>
       <c r="C6" t="n">
-        <v>6.309516621738942</v>
+        <v>34.44067362871986</v>
       </c>
       <c r="D6" t="n">
-        <v>104.5</v>
+        <v>109</v>
       </c>
       <c r="E6" t="n">
-        <v>4.759201613716317</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25.71380951940027</v>
+      </c>
+      <c r="H6" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25.53448648396909</v>
+      </c>
+      <c r="J6" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.135415650406262</v>
+      </c>
+      <c r="L6" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>110</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.732050807568877</v>
+      </c>
+      <c r="P6" t="n">
         <v>109.7</v>
       </c>
-      <c r="G6" t="n">
-        <v>6.957729514719583</v>
-      </c>
-      <c r="H6" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6.036555309114628</v>
-      </c>
-      <c r="J6" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.014983962918233</v>
-      </c>
-      <c r="L6" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.854723699099141</v>
-      </c>
-      <c r="N6" t="n">
-        <v>115</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.569046515733026</v>
-      </c>
-      <c r="P6" t="n">
-        <v>111</v>
-      </c>
       <c r="Q6" t="n">
-        <v>7.334848328356899</v>
+        <v>1.1</v>
       </c>
       <c r="R6" t="n">
-        <v>113.5</v>
+        <v>109.1</v>
       </c>
       <c r="S6" t="n">
-        <v>5.463515351859094</v>
+        <v>2.426932219902319</v>
       </c>
       <c r="T6" t="n">
-        <v>111.8</v>
+        <v>109.9</v>
       </c>
       <c r="U6" t="n">
-        <v>6.939740629158989</v>
+        <v>2.586503431275513</v>
       </c>
       <c r="V6" t="n">
-        <v>117</v>
+        <v>110.2</v>
       </c>
       <c r="W6" t="n">
-        <v>4.074309757492673</v>
+        <v>2.135415650406262</v>
       </c>
       <c r="X6" t="n">
-        <v>110.5</v>
+        <v>109.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.868483523128406</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>105.9</v>
+        <v>111.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.395832299420945</v>
+        <v>1.939071942966532</v>
       </c>
       <c r="AB6" t="n">
-        <v>109.5</v>
+        <v>110.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.357631243360764</v>
+        <v>1.98997487421324</v>
       </c>
       <c r="AD6" t="n">
-        <v>107.8</v>
+        <v>110.6</v>
       </c>
       <c r="AE6" t="n">
-        <v>9.053176238205021</v>
+        <v>1.743559577416269</v>
       </c>
       <c r="AF6" t="n">
-        <v>107.4</v>
+        <v>111.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.13114011353115</v>
+        <v>3.091924966748062</v>
       </c>
       <c r="AH6" t="n">
-        <v>107.5</v>
+        <v>112.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.324616030891995</v>
+        <v>2.147091055358389</v>
       </c>
       <c r="AJ6" t="n">
-        <v>109.9</v>
+        <v>113.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>10.8023145667954</v>
+        <v>2.256102834535695</v>
       </c>
       <c r="AL6" t="n">
-        <v>100.4</v>
+        <v>113.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.788629017087933</v>
+        <v>2.271563338320109</v>
       </c>
       <c r="AN6" t="n">
-        <v>101.6</v>
+        <v>114.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>7.472616676907761</v>
+        <v>2.758622844826744</v>
       </c>
       <c r="AP6" t="n">
-        <v>105.7</v>
+        <v>117.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.694027188471824</v>
+        <v>2.165640782770772</v>
       </c>
       <c r="AR6" t="n">
-        <v>99.90000000000001</v>
+        <v>120</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.48543526076099</v>
+        <v>6.260990336999411</v>
       </c>
       <c r="AT6" t="n">
-        <v>98.3</v>
+        <v>119.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.629547824084989</v>
+        <v>1.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>102.1</v>
+        <v>121</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.769748694700662</v>
+        <v>6.115553940568262</v>
       </c>
       <c r="AX6" t="n">
-        <v>100.7</v>
+        <v>122.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.466065264130885</v>
+        <v>5.514526271584894</v>
       </c>
       <c r="AZ6" t="n">
-        <v>101.3</v>
+        <v>121.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.360045871318328</v>
+        <v>1.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>104.1</v>
+        <v>129</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.487680633323437</v>
+        <v>7.987490219086343</v>
       </c>
       <c r="BD6" t="n">
-        <v>105.3</v>
+        <v>134.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.017474553332153</v>
+        <v>11.09098733206381</v>
       </c>
       <c r="BF6" t="n">
-        <v>103.1</v>
+        <v>136.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.251666498350501</v>
+        <v>10.14347080638575</v>
       </c>
       <c r="BH6" t="n">
-        <v>104</v>
+        <v>132.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>5.157518783291051</v>
+        <v>9.297311439335568</v>
       </c>
       <c r="BJ6" t="n">
-        <v>3205.9</v>
+        <v>3429.1</v>
       </c>
       <c r="BK6" t="n">
-        <v>106.8633333333333</v>
+        <v>114.3033333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1705,190 +1705,190 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>103.1</v>
+        <v>99.5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.256102834535695</v>
+        <v>26.94902595642373</v>
       </c>
       <c r="D7" t="n">
-        <v>106.9</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>4.825971404805461</v>
+        <v>35.7468879764379</v>
       </c>
       <c r="F7" t="n">
-        <v>103.9</v>
+        <v>108.7</v>
       </c>
       <c r="G7" t="n">
-        <v>8.154140052758477</v>
+        <v>1.615549442140351</v>
       </c>
       <c r="H7" t="n">
-        <v>110.2</v>
+        <v>100.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.30659966456864</v>
+        <v>25.62498780487515</v>
       </c>
       <c r="J7" t="n">
-        <v>113.4</v>
+        <v>109.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.374868417407583</v>
+        <v>2.325940669922601</v>
       </c>
       <c r="L7" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.746424919657298</v>
+      </c>
+      <c r="N7" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.067572330035594</v>
+      </c>
+      <c r="P7" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.685229954635272</v>
+      </c>
+      <c r="R7" t="n">
+        <v>109</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.408318915758459</v>
+      </c>
+      <c r="T7" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.9433981132056604</v>
+      </c>
+      <c r="V7" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.907878402833891</v>
+      </c>
+      <c r="X7" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.712931993250108</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.315167380558045</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.734935157289747</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.609597670139978</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.764054992217051</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>112.8</v>
       </c>
-      <c r="M7" t="n">
-        <v>5.617828762075256</v>
-      </c>
-      <c r="N7" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.202271554554524</v>
-      </c>
-      <c r="P7" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.513274595042156</v>
-      </c>
-      <c r="R7" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.709447398198281</v>
-      </c>
-      <c r="T7" t="n">
-        <v>111</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8.831760866327848</v>
-      </c>
-      <c r="V7" t="n">
-        <v>106.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>7.733692520394123</v>
-      </c>
-      <c r="X7" t="n">
-        <v>109.2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11.68588892639323</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>6.469157595854347</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.748548251124206</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>107.7</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>5.797413216254298</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>108</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>8.865664103720601</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>8.239538822045807</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>105</v>
-      </c>
       <c r="AK7" t="n">
-        <v>9.143303560529969</v>
+        <v>1.939071942966532</v>
       </c>
       <c r="AL7" t="n">
-        <v>105.7</v>
+        <v>114.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>10.41201229350023</v>
+        <v>2.0591260281974</v>
       </c>
       <c r="AN7" t="n">
-        <v>102.2</v>
+        <v>116.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.925315877272314</v>
+        <v>3.280243893371345</v>
       </c>
       <c r="AP7" t="n">
-        <v>100.8</v>
+        <v>116.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.896834808959853</v>
+        <v>1.920937271229854</v>
       </c>
       <c r="AR7" t="n">
-        <v>103.2</v>
+        <v>115.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.670978751503131</v>
+        <v>1.688194301613413</v>
       </c>
       <c r="AT7" t="n">
-        <v>99.90000000000001</v>
+        <v>120.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.504442251822083</v>
+        <v>5.923681287847955</v>
       </c>
       <c r="AV7" t="n">
-        <v>100.8</v>
+        <v>119.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.939740629158989</v>
+        <v>1.445683229480096</v>
       </c>
       <c r="AX7" t="n">
-        <v>99.7</v>
+        <v>123.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.657738063926255</v>
+        <v>6.086049621881176</v>
       </c>
       <c r="AZ7" t="n">
-        <v>98.3</v>
+        <v>124.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.348133808556641</v>
+        <v>6.063002556489647</v>
       </c>
       <c r="BB7" t="n">
-        <v>102.5</v>
+        <v>126.7</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.631414470763764</v>
+        <v>2.865309756378881</v>
       </c>
       <c r="BD7" t="n">
-        <v>104.9</v>
+        <v>130.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.481033698917011</v>
+        <v>8.154140052758475</v>
       </c>
       <c r="BF7" t="n">
-        <v>101.5</v>
+        <v>137.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.426785420486054</v>
+        <v>9.457801012920498</v>
       </c>
       <c r="BH7" t="n">
-        <v>105</v>
+        <v>139.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>7.05691150575094</v>
+        <v>8.231646250902671</v>
       </c>
       <c r="BJ7" t="n">
-        <v>3185</v>
+        <v>3432.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>106.1666666666667</v>
+        <v>114.4133333333333</v>
       </c>
     </row>
     <row r="8">
@@ -1896,190 +1896,190 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>106.9</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>4.678675026115834</v>
+        <v>35.8</v>
       </c>
       <c r="D8" t="n">
-        <v>105.9</v>
+        <v>108.6</v>
       </c>
       <c r="E8" t="n">
-        <v>7.327346040688948</v>
+        <v>2.576819745345025</v>
       </c>
       <c r="F8" t="n">
-        <v>108.4</v>
+        <v>98.7</v>
       </c>
       <c r="G8" t="n">
-        <v>3.903844259188627</v>
+        <v>25.95399776527693</v>
       </c>
       <c r="H8" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25.54701548126512</v>
+      </c>
+      <c r="J8" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.156385865284783</v>
+      </c>
+      <c r="L8" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.002498439450079</v>
+      </c>
+      <c r="N8" t="n">
         <v>109.7</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.648655719667784</v>
-      </c>
-      <c r="J8" t="n">
-        <v>107</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9.273618495495704</v>
-      </c>
-      <c r="L8" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.486606874731851</v>
-      </c>
-      <c r="N8" t="n">
-        <v>114.7</v>
-      </c>
       <c r="O8" t="n">
-        <v>4.148493702538308</v>
+        <v>2.570992026436488</v>
       </c>
       <c r="P8" t="n">
-        <v>112.2</v>
+        <v>107.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.894895300208167</v>
+        <v>2.118962010041709</v>
       </c>
       <c r="R8" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.86815416922694</v>
+      </c>
+      <c r="T8" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.08806130178211</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.211334438749598</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.813835714721705</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.22065556157337</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.734935157289747</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2.491987158875423</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.624807680927192</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.85472369909914</v>
+      </c>
+      <c r="AP8" t="n">
         <v>115.3</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.226453160980336</v>
-      </c>
-      <c r="T8" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6.569627082262737</v>
-      </c>
-      <c r="V8" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>8.485870609430714</v>
-      </c>
-      <c r="X8" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5.762811813689564</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>111.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>6.315853069855251</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.72194012294417</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>108.9</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>9.428149341201591</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>6.756478372643548</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>108.8</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8.072174428244226</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>7.327346040688948</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>7.952986860293433</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>8.665448632355972</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>102.7</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>5.780138406647371</v>
+        <v>1.734935157289747</v>
       </c>
       <c r="AR8" t="n">
-        <v>98.09999999999999</v>
+        <v>119.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.988987873306568</v>
+        <v>6.245798587850876</v>
       </c>
       <c r="AT8" t="n">
-        <v>102.6</v>
+        <v>119.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.748548251124206</v>
+        <v>1.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>104.5</v>
+        <v>119.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.024937810560445</v>
+        <v>2.165640782770772</v>
       </c>
       <c r="AX8" t="n">
-        <v>104.7</v>
+        <v>124.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.780138406647371</v>
+        <v>6.305553108173779</v>
       </c>
       <c r="AZ8" t="n">
-        <v>102.7</v>
+        <v>124.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.728001396647874</v>
+        <v>6.523802572120037</v>
       </c>
       <c r="BB8" t="n">
-        <v>102.5</v>
+        <v>130.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.447221813845593</v>
+        <v>9.843271813782245</v>
       </c>
       <c r="BD8" t="n">
-        <v>104.5</v>
+        <v>128.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.48459713474939</v>
+        <v>5.287721626560915</v>
       </c>
       <c r="BF8" t="n">
-        <v>101.7</v>
+        <v>139</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.341135544995075</v>
+        <v>10.06975670013928</v>
       </c>
       <c r="BH8" t="n">
-        <v>105.5</v>
+        <v>141.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>5.445181356024793</v>
+        <v>9.350935782048767</v>
       </c>
       <c r="BJ8" t="n">
-        <v>3212.899999999999</v>
+        <v>3437.200000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>107.0966666666666</v>
+        <v>114.5733333333334</v>
       </c>
     </row>
     <row r="9">
@@ -2087,190 +2087,190 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>107.6</v>
+        <v>72.5</v>
       </c>
       <c r="C9" t="n">
-        <v>6.135144660071187</v>
+        <v>43.52298243457128</v>
       </c>
       <c r="D9" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33.92064268259079</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26.17269569608755</v>
+      </c>
+      <c r="H9" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.118962010041709</v>
+      </c>
+      <c r="J9" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>25.4825430442097</v>
+      </c>
+      <c r="L9" t="n">
         <v>109.8</v>
       </c>
-      <c r="E9" t="n">
-        <v>5.912698199637793</v>
-      </c>
-      <c r="F9" t="n">
-        <v>108.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.487119154832539</v>
-      </c>
-      <c r="H9" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.605431575867782</v>
-      </c>
-      <c r="J9" t="n">
-        <v>108.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9.075241043630742</v>
-      </c>
-      <c r="L9" t="n">
-        <v>113.4</v>
-      </c>
       <c r="M9" t="n">
-        <v>2.690724809414742</v>
+        <v>1.536229149573722</v>
       </c>
       <c r="N9" t="n">
-        <v>114.3</v>
+        <v>110.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.282542442102666</v>
+        <v>2.418677324489565</v>
       </c>
       <c r="P9" t="n">
-        <v>116.2</v>
+        <v>109.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.886796226411321</v>
+        <v>1.743559577416269</v>
       </c>
       <c r="R9" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.193171219946131</v>
+      </c>
+      <c r="T9" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.051828452868319</v>
+      </c>
+      <c r="V9" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.238302928559939</v>
+      </c>
+      <c r="X9" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.0591260281974</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.009975124224178</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.758622844826745</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>111.6</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.86815416922694</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.536229149573722</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.118962010041709</v>
+      </c>
+      <c r="AL9" t="n">
         <v>114.5</v>
       </c>
-      <c r="S9" t="n">
-        <v>6.328506932918696</v>
-      </c>
-      <c r="T9" t="n">
-        <v>114.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4.409081537009721</v>
-      </c>
-      <c r="V9" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.592385001282013</v>
-      </c>
-      <c r="X9" t="n">
-        <v>111</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>7.293833011524188</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>7.785242449660768</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.163332652783421</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>111</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>8.461678320522472</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>7.267048919609665</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>105.7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>8.474078120952154</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>9.818859404228172</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>100.4</v>
-      </c>
       <c r="AM9" t="n">
-        <v>7.644605941446557</v>
+        <v>1.565247584249853</v>
       </c>
       <c r="AN9" t="n">
-        <v>102.2</v>
+        <v>115</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.05407683541936</v>
+        <v>2.756809750418044</v>
       </c>
       <c r="AP9" t="n">
-        <v>99</v>
+        <v>115.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.577708763999663</v>
+        <v>1.469693845669907</v>
       </c>
       <c r="AR9" t="n">
-        <v>101.5</v>
+        <v>117.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.671375365604267</v>
+        <v>2.238302928559939</v>
       </c>
       <c r="AT9" t="n">
-        <v>102</v>
+        <v>119.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.962411694957753</v>
+        <v>1.91049731745428</v>
       </c>
       <c r="AV9" t="n">
-        <v>100.1</v>
+        <v>122.9</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.189575787207477</v>
+        <v>5.629387178015027</v>
       </c>
       <c r="AX9" t="n">
-        <v>103.4</v>
+        <v>120.7</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.418894796396563</v>
+        <v>1.417744687875782</v>
       </c>
       <c r="AZ9" t="n">
-        <v>103.8</v>
+        <v>127.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.660330322138686</v>
+        <v>9.004998611882181</v>
       </c>
       <c r="BB9" t="n">
-        <v>102.7</v>
+        <v>126.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.165225056719342</v>
+        <v>8.255906976220118</v>
       </c>
       <c r="BD9" t="n">
-        <v>103</v>
+        <v>132.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.230384607371461</v>
+        <v>9.378699270154684</v>
       </c>
       <c r="BF9" t="n">
-        <v>99</v>
+        <v>132.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.768288736283354</v>
+        <v>10.78378412246833</v>
       </c>
       <c r="BH9" t="n">
-        <v>102.6</v>
+        <v>123.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>6.988562083862459</v>
+        <v>32.96907642018503</v>
       </c>
       <c r="BJ9" t="n">
-        <v>3206.5</v>
+        <v>3378.399999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>106.8833333333333</v>
+        <v>112.6133333333333</v>
       </c>
     </row>
     <row r="10">
@@ -2278,190 +2278,190 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>102.1</v>
+        <v>89.5</v>
       </c>
       <c r="C10" t="n">
-        <v>3.299999999999999</v>
+        <v>35.54222840509582</v>
       </c>
       <c r="D10" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>39.73713628333073</v>
+      </c>
+      <c r="F10" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.562049935181331</v>
+      </c>
+      <c r="H10" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.135415650406262</v>
+      </c>
+      <c r="J10" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.959591794226542</v>
+      </c>
+      <c r="L10" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.813835714721705</v>
+      </c>
+      <c r="N10" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.685229954635272</v>
+      </c>
+      <c r="P10" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R10" t="n">
         <v>108.7</v>
       </c>
-      <c r="E10" t="n">
-        <v>4.94064773081425</v>
-      </c>
-      <c r="F10" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5.445181356024793</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="S10" t="n">
+        <v>1.345362404707371</v>
+      </c>
+      <c r="T10" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>111</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.04939015319192</v>
+      </c>
+      <c r="X10" t="n">
         <v>110.1</v>
       </c>
-      <c r="I10" t="n">
-        <v>6.729784543356496</v>
-      </c>
-      <c r="J10" t="n">
-        <v>111.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.714017850864661</v>
-      </c>
-      <c r="L10" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.530696746902279</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="Y10" t="n">
+        <v>1.640121946685672</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.939071942966532</v>
+      </c>
+      <c r="AD10" t="n">
         <v>112.8</v>
       </c>
-      <c r="O10" t="n">
-        <v>6.368673331236264</v>
-      </c>
-      <c r="P10" t="n">
-        <v>116.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.609597670139978</v>
-      </c>
-      <c r="R10" t="n">
-        <v>115.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8.212186067059124</v>
-      </c>
-      <c r="T10" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="U10" t="n">
-        <v>7.912648102879339</v>
-      </c>
-      <c r="V10" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>5.044799302251775</v>
-      </c>
-      <c r="X10" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>8.642337646724988</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>108.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>9.489467845985885</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>6.974955196988724</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>110.3</v>
-      </c>
       <c r="AE10" t="n">
-        <v>7.563729238940272</v>
+        <v>1.98997487421324</v>
       </c>
       <c r="AF10" t="n">
-        <v>107.5</v>
+        <v>111</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.09207609959418</v>
+        <v>2.529822128134704</v>
       </c>
       <c r="AH10" t="n">
-        <v>104.9</v>
+        <v>111.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>8.848163651289457</v>
+        <v>1.486606874731851</v>
       </c>
       <c r="AJ10" t="n">
-        <v>104.8</v>
+        <v>112.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>7.291090453423274</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>103</v>
+        <v>114.7</v>
       </c>
       <c r="AM10" t="n">
-        <v>7.771743691090179</v>
+        <v>2.758622844826744</v>
       </c>
       <c r="AN10" t="n">
-        <v>106.5</v>
+        <v>117.2</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.35615758860399</v>
+        <v>6.161168720299744</v>
       </c>
       <c r="AP10" t="n">
-        <v>99</v>
+        <v>116.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.681145747868608</v>
+        <v>2.56124969497314</v>
       </c>
       <c r="AR10" t="n">
-        <v>105.1</v>
+        <v>117</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.514105942493316</v>
+        <v>3</v>
       </c>
       <c r="AT10" t="n">
-        <v>97.90000000000001</v>
+        <v>122.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.678675026115834</v>
+        <v>6.017474553332153</v>
       </c>
       <c r="AV10" t="n">
-        <v>101.6</v>
+        <v>124.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.219195340279955</v>
+        <v>7.968061244744546</v>
       </c>
       <c r="AX10" t="n">
-        <v>101</v>
+        <v>123.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.291502622129181</v>
+        <v>6.468384651518493</v>
       </c>
       <c r="AZ10" t="n">
-        <v>98.90000000000001</v>
+        <v>122.6</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.570557952810575</v>
+        <v>2.497999199359359</v>
       </c>
       <c r="BB10" t="n">
-        <v>102</v>
+        <v>128.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.878524367060187</v>
+        <v>8.212794895770866</v>
       </c>
       <c r="BD10" t="n">
-        <v>102.2</v>
+        <v>133.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.584831053261731</v>
+        <v>7.927168473042565</v>
       </c>
       <c r="BF10" t="n">
-        <v>103.5</v>
+        <v>138.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.389805191284746</v>
+        <v>11.11260545506768</v>
       </c>
       <c r="BH10" t="n">
-        <v>104.6</v>
+        <v>136.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.642694391866355</v>
+        <v>11.44377560073597</v>
       </c>
       <c r="BJ10" t="n">
-        <v>3205.199999999999</v>
+        <v>3429.299999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>106.84</v>
+        <v>114.31</v>
       </c>
     </row>
     <row r="11">
@@ -2469,190 +2469,190 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>107.9</v>
+        <v>89.2</v>
       </c>
       <c r="C11" t="n">
-        <v>6.594694837519018</v>
+        <v>35.42259166125482</v>
       </c>
       <c r="D11" t="n">
-        <v>106.9</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>5.57584074378026</v>
+        <v>25.85904097216291</v>
       </c>
       <c r="F11" t="n">
-        <v>106.9</v>
+        <v>100.6</v>
       </c>
       <c r="G11" t="n">
-        <v>5.412023651093923</v>
+        <v>25.90443977390748</v>
       </c>
       <c r="H11" t="n">
-        <v>107.1</v>
+        <v>109.4</v>
       </c>
       <c r="I11" t="n">
-        <v>6.122907805936653</v>
+        <v>2.33238075793812</v>
       </c>
       <c r="J11" t="n">
-        <v>111.8</v>
+        <v>109.5</v>
       </c>
       <c r="K11" t="n">
-        <v>7.372923436466705</v>
+        <v>2.012461179749811</v>
       </c>
       <c r="L11" t="n">
-        <v>108.1</v>
+        <v>108.6</v>
       </c>
       <c r="M11" t="n">
-        <v>8.926925562588725</v>
+        <v>2.107130750570548</v>
       </c>
       <c r="N11" t="n">
-        <v>109.6</v>
+        <v>109.5</v>
       </c>
       <c r="O11" t="n">
-        <v>10.50904372433572</v>
+        <v>2.109502310972899</v>
       </c>
       <c r="P11" t="n">
-        <v>114.4</v>
+        <v>109.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.624944444170094</v>
+        <v>2.282542442102665</v>
       </c>
       <c r="R11" t="n">
-        <v>116</v>
+        <v>109.7</v>
       </c>
       <c r="S11" t="n">
-        <v>2.144761058952722</v>
+        <v>3.001666203960727</v>
       </c>
       <c r="T11" t="n">
-        <v>112.9</v>
+        <v>110.4</v>
       </c>
       <c r="U11" t="n">
-        <v>4.988987873306568</v>
+        <v>2.33238075793812</v>
       </c>
       <c r="V11" t="n">
-        <v>108.6</v>
+        <v>110.1</v>
       </c>
       <c r="W11" t="n">
-        <v>8.867919710958146</v>
+        <v>1.972308292331602</v>
       </c>
       <c r="X11" t="n">
-        <v>110.4</v>
+        <v>109.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.031358332498779</v>
+        <v>2.06155281280883</v>
       </c>
       <c r="Z11" t="n">
-        <v>104.7</v>
+        <v>110.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.379140767405689</v>
+        <v>2.06155281280883</v>
       </c>
       <c r="AB11" t="n">
-        <v>110.4</v>
+        <v>110.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.08801805866774</v>
+        <v>2.481934729198171</v>
       </c>
       <c r="AD11" t="n">
-        <v>106.5</v>
+        <v>112.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>7.864477096412704</v>
+        <v>1.42828568570857</v>
       </c>
       <c r="AF11" t="n">
-        <v>104.6</v>
+        <v>112.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.735631842325486</v>
+        <v>1.846618531261939</v>
       </c>
       <c r="AH11" t="n">
-        <v>101.6</v>
+        <v>113</v>
       </c>
       <c r="AI11" t="n">
-        <v>9.046546302318914</v>
+        <v>1.673320053068151</v>
       </c>
       <c r="AJ11" t="n">
-        <v>107.7</v>
+        <v>112.4</v>
       </c>
       <c r="AK11" t="n">
-        <v>8.307225770376053</v>
+        <v>2.0591260281974</v>
       </c>
       <c r="AL11" t="n">
-        <v>101.6</v>
+        <v>112.3</v>
       </c>
       <c r="AM11" t="n">
-        <v>8.428523002282191</v>
+        <v>1.615549442140351</v>
       </c>
       <c r="AN11" t="n">
-        <v>100.7</v>
+        <v>115.7</v>
       </c>
       <c r="AO11" t="n">
-        <v>7.22564875980005</v>
+        <v>2.147091055358389</v>
       </c>
       <c r="AP11" t="n">
-        <v>103.6</v>
+        <v>117.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.840731680114036</v>
+        <v>6.135144660071187</v>
       </c>
       <c r="AR11" t="n">
-        <v>99.3</v>
+        <v>117.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.436568055487917</v>
+        <v>1.907878402833891</v>
       </c>
       <c r="AT11" t="n">
-        <v>98.7</v>
+        <v>119.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.754997371187496</v>
+        <v>2.271563338320109</v>
       </c>
       <c r="AV11" t="n">
-        <v>101.3</v>
+        <v>120.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.561797891182818</v>
+        <v>1.486606874731851</v>
       </c>
       <c r="AX11" t="n">
-        <v>102.4</v>
+        <v>125.1</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.82078831727758</v>
+        <v>7.217340230306452</v>
       </c>
       <c r="AZ11" t="n">
-        <v>103.1</v>
+        <v>126.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.378871373526825</v>
+        <v>6.876772498781678</v>
       </c>
       <c r="BB11" t="n">
-        <v>109.8</v>
+        <v>137.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.11228271597445</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BD11" t="n">
-        <v>104</v>
+        <v>120.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.131883886702357</v>
+        <v>32.31857051294194</v>
       </c>
       <c r="BF11" t="n">
-        <v>98.7</v>
+        <v>134.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.075536774462967</v>
+        <v>9.907572861200668</v>
       </c>
       <c r="BH11" t="n">
-        <v>104.6</v>
+        <v>133.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>5.868560300448484</v>
+        <v>8.535221145348256</v>
       </c>
       <c r="BJ11" t="n">
-        <v>3183.9</v>
+        <v>3429.3</v>
       </c>
       <c r="BK11" t="n">
-        <v>106.13</v>
+        <v>114.31</v>
       </c>
     </row>
   </sheetData>
